--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3737,6 +3737,117 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127413625</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Södra Fingerboda, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>507039</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6593318</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Emil Pagstedt Andersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92644</v>
+        <v>92648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>127413625</v>
       </c>
       <c r="B27" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3848,6 +3848,130 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129201495</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98659</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mariedal, Mariedal, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>507076</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6593399</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Camilla Pettersson, Ankie Rauséus, Lotta Sörman, Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 11286-2021 artfynd.xlsx
+++ b/artfynd/A 11286-2021 artfynd.xlsx
@@ -3853,7 +3853,7 @@
         <v>129201495</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
